--- a/2026-06/R8祭礼予算・進行表.xlsx
+++ b/2026-06/R8祭礼予算・進行表.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/951bde4d8205714a/ドキュメント/komatest/2026-06/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/951bde4d8205714a/◆駒寄◆/㉑祭礼/R8祭礼/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{411F52D3-0B82-4718-BF6F-1DE46E09691D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35EDB504-D33C-4B4B-98DC-873A71DBC63C}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="13_ncr:1_{411F52D3-0B82-4718-BF6F-1DE46E09691D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBAAF133-7688-49CE-96A6-479034061F6D}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="180" windowWidth="17790" windowHeight="13725" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4260" yWindow="990" windowWidth="17790" windowHeight="13725" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="①宵宮祭rev.F" sheetId="29" r:id="rId1"/>
-    <sheet name="②本祭rev.F" sheetId="30" r:id="rId2"/>
+    <sheet name="①宵宮祭rev.G" sheetId="29" r:id="rId1"/>
+    <sheet name="②本祭rev.G" sheetId="30" r:id="rId2"/>
     <sheet name="R6 収支計画" sheetId="26" r:id="rId3"/>
     <sheet name="R5年度祭礼予算計画シミュレーション" sheetId="1" r:id="rId4"/>
     <sheet name="実績メモ" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'①宵宮祭rev.F'!$A$1:$K$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'②本祭rev.F'!$A$1:$K$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">①宵宮祭rev.G!$A$1:$K$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">②本祭rev.G!$A$1:$K$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +64,7 @@
           <t>・伊藤大樹（代表）
 ・佐野竜斗
 ・佐野翔斗
-・橋本雲千代 ※土曜不在
+・橋本雲千代
 ・稲橋完久朗　（交通）</t>
         </r>
       </text>
@@ -620,7 +620,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="342">
   <si>
     <t>収入</t>
     <rPh sb="0" eb="2">
@@ -2706,14 +2706,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>③軍司邸前</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>④赤荻邸前</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>54</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3961,6 +3953,30 @@
   </si>
   <si>
     <t>③会館到着（11:00）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③伊藤邸前</t>
+    <rPh sb="1" eb="3">
+      <t>イトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（休憩） 松村邸前</t>
+    <rPh sb="5" eb="7">
+      <t>マツムラ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④軍司邸前</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -22665,7 +22681,7 @@
     <row r="7" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="265"/>
       <c r="D7" s="313" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E7" s="129"/>
       <c r="F7" s="265"/>
@@ -22681,7 +22697,7 @@
         <v>180</v>
       </c>
       <c r="D8" s="315" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E8" s="246"/>
       <c r="F8" s="252" t="s">
@@ -22695,7 +22711,7 @@
         <v>180</v>
       </c>
       <c r="J8" s="318" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -22709,7 +22725,7 @@
       <c r="H9" s="91"/>
       <c r="I9" s="86"/>
       <c r="J9" s="91" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -22721,7 +22737,7 @@
       <c r="H10" s="85"/>
       <c r="I10" s="86"/>
       <c r="J10" s="85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -22768,7 +22784,7 @@
       <c r="E15" s="130"/>
       <c r="F15" s="366"/>
       <c r="G15" s="130" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H15" s="130"/>
       <c r="I15" s="278"/>
@@ -22792,7 +22808,7 @@
       <c r="E17" s="323"/>
       <c r="F17" s="324"/>
       <c r="G17" s="328" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H17" s="323"/>
       <c r="I17" s="325"/>
@@ -22803,7 +22819,7 @@
         <v>180</v>
       </c>
       <c r="D18" s="290" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E18" s="130"/>
       <c r="F18" s="252"/>
@@ -22842,7 +22858,7 @@
       <c r="E21" s="85"/>
       <c r="F21" s="95"/>
       <c r="G21" s="251" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H21" s="89"/>
       <c r="I21" s="88"/>
@@ -22960,12 +22976,12 @@
       <c r="E28" s="85"/>
       <c r="F28" s="304"/>
       <c r="G28" s="166" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H28" s="85"/>
       <c r="I28" s="259"/>
       <c r="J28" s="210" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -22993,7 +23009,7 @@
         <v>181</v>
       </c>
       <c r="D30" s="102" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E30" s="85"/>
       <c r="F30" s="88"/>
@@ -23011,7 +23027,7 @@
         <v>182</v>
       </c>
       <c r="D31" s="102" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E31" s="85"/>
       <c r="F31" s="88"/>
@@ -23029,7 +23045,7 @@
         <v>183</v>
       </c>
       <c r="D32" s="102" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E32" s="89"/>
       <c r="F32" s="88"/>
@@ -23037,7 +23053,7 @@
       <c r="H32" s="93"/>
       <c r="I32" s="167"/>
       <c r="J32" s="191" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23045,7 +23061,7 @@
         <v>212</v>
       </c>
       <c r="D33" s="136" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E33" s="129"/>
       <c r="F33" s="261"/>
@@ -23061,7 +23077,7 @@
         <v>186</v>
       </c>
       <c r="D34" s="258" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E34" s="130"/>
       <c r="F34" s="252"/>
@@ -23077,7 +23093,7 @@
     <row r="35" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C35" s="160"/>
       <c r="D35" s="102" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E35" s="85"/>
       <c r="F35" s="88"/>
@@ -23091,7 +23107,7 @@
         <v>187</v>
       </c>
       <c r="D36" s="102" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E36" s="85"/>
       <c r="F36" s="260"/>
@@ -23105,7 +23121,7 @@
         <v>191</v>
       </c>
       <c r="D37" s="102" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E37" s="85"/>
       <c r="F37" s="88"/>
@@ -23119,7 +23135,7 @@
         <v>181</v>
       </c>
       <c r="D38" s="102" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E38" s="85"/>
       <c r="F38" s="88"/>
@@ -23131,7 +23147,7 @@
     <row r="39" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C39" s="133"/>
       <c r="D39" s="264" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E39" s="129"/>
       <c r="F39" s="261"/>
@@ -23148,12 +23164,12 @@
         <v>180</v>
       </c>
       <c r="G40" s="269" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H40" s="130"/>
       <c r="I40" s="270"/>
       <c r="J40" s="221" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23167,7 +23183,7 @@
         <v>187</v>
       </c>
       <c r="J41" s="365" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23182,7 +23198,7 @@
       <c r="H42" s="87"/>
       <c r="I42" s="106"/>
       <c r="J42" s="177" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23193,7 +23209,7 @@
         <v>182</v>
       </c>
       <c r="G43" s="272" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H43" s="132"/>
       <c r="I43" s="273"/>
@@ -23207,7 +23223,7 @@
         <v>187</v>
       </c>
       <c r="G44" s="334" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H44" s="249"/>
       <c r="I44" s="334"/>
@@ -23219,7 +23235,7 @@
       <c r="E45" s="85"/>
       <c r="F45" s="308"/>
       <c r="G45" s="192" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H45" s="85"/>
       <c r="I45" s="168"/>
@@ -23233,7 +23249,7 @@
         <v>192</v>
       </c>
       <c r="G46" s="169" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="169"/>
@@ -23245,7 +23261,7 @@
       <c r="E47" s="85"/>
       <c r="F47" s="307"/>
       <c r="G47" s="193" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H47" s="85"/>
       <c r="I47" s="168"/>
@@ -23257,7 +23273,7 @@
       <c r="E48" s="129"/>
       <c r="F48" s="309"/>
       <c r="G48" s="275" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H48" s="129"/>
       <c r="I48" s="276"/>
@@ -23271,7 +23287,7 @@
         <v>186</v>
       </c>
       <c r="G49" s="279" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H49" s="267"/>
       <c r="I49" s="279"/>
@@ -23283,7 +23299,7 @@
       <c r="E50" s="85"/>
       <c r="F50" s="307"/>
       <c r="G50" s="193" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H50" s="170"/>
       <c r="I50" s="171"/>
@@ -23297,7 +23313,7 @@
         <v>191</v>
       </c>
       <c r="G51" s="174" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="169"/>
@@ -23309,14 +23325,14 @@
       <c r="E52" s="85"/>
       <c r="F52" s="310"/>
       <c r="G52" s="194" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H52" s="94"/>
       <c r="I52" s="305" t="s">
         <v>181</v>
       </c>
       <c r="J52" s="174" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23327,7 +23343,7 @@
         <v>182</v>
       </c>
       <c r="G53" s="193" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H53" s="284"/>
       <c r="I53" s="163"/>
@@ -23339,12 +23355,12 @@
       <c r="E54" s="129"/>
       <c r="F54" s="306"/>
       <c r="G54" s="285" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H54" s="131"/>
       <c r="I54" s="280"/>
       <c r="J54" s="281" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23353,7 +23369,7 @@
       <c r="E55" s="262"/>
       <c r="F55" s="311"/>
       <c r="G55" s="286" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H55" s="130"/>
       <c r="I55" s="278"/>
@@ -23546,7 +23562,7 @@
         <v>181</v>
       </c>
       <c r="G4" s="86" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H4" s="87"/>
       <c r="I4" s="107"/>
@@ -23567,14 +23583,14 @@
     <row r="6" spans="3:14" ht="20.100000000000001" customHeight="1">
       <c r="C6" s="212"/>
       <c r="D6" s="213" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E6" s="85"/>
       <c r="F6" s="295" t="s">
         <v>182</v>
       </c>
       <c r="G6" s="296" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H6" s="85"/>
       <c r="I6" s="107"/>
@@ -23583,7 +23599,7 @@
     <row r="7" spans="3:14" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="138"/>
       <c r="D7" s="139" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E7" s="129"/>
       <c r="F7" s="297"/>
@@ -23597,7 +23613,7 @@
         <v>180</v>
       </c>
       <c r="D8" s="347" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E8" s="130"/>
       <c r="F8" s="208" t="s">
@@ -23616,7 +23632,7 @@
         <v>181</v>
       </c>
       <c r="D9" s="136" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E9" s="85"/>
       <c r="F9" s="107"/>
@@ -23629,10 +23645,10 @@
     </row>
     <row r="10" spans="3:14" ht="20.100000000000001" customHeight="1">
       <c r="C10" s="216" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D10" s="111" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E10" s="85"/>
       <c r="F10" s="109"/>
@@ -23646,25 +23662,25 @@
         <v>193</v>
       </c>
       <c r="D11" s="110" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E11" s="85"/>
       <c r="F11" s="118"/>
       <c r="G11" s="176" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H11" s="109"/>
       <c r="I11" s="209"/>
       <c r="J11" s="210" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="3:14" ht="20.100000000000001" customHeight="1">
       <c r="C12" s="138" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D12" s="155" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E12" s="129"/>
       <c r="F12" s="299" t="s">
@@ -23686,7 +23702,7 @@
         <v>184</v>
       </c>
       <c r="D13" s="347" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="202" t="s">
@@ -23700,7 +23716,7 @@
         <v>180</v>
       </c>
       <c r="J13" s="355" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="3:14" ht="20.100000000000001" customHeight="1">
@@ -23708,15 +23724,17 @@
         <v>194</v>
       </c>
       <c r="D14" s="110" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E14" s="85"/>
       <c r="F14" s="118"/>
-      <c r="G14" s="201"/>
+      <c r="G14" s="201" t="s">
+        <v>329</v>
+      </c>
       <c r="H14" s="109"/>
       <c r="I14" s="178"/>
       <c r="J14" s="360" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="3:14" ht="20.100000000000001" customHeight="1">
@@ -23724,17 +23742,17 @@
         <v>195</v>
       </c>
       <c r="D15" s="111" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E15" s="85"/>
       <c r="F15" s="118"/>
       <c r="G15" s="201" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H15" s="109"/>
       <c r="I15" s="178"/>
       <c r="J15" s="211" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="3:14" ht="20.100000000000001" customHeight="1">
@@ -23743,12 +23761,12 @@
       <c r="E16" s="85"/>
       <c r="F16" s="118"/>
       <c r="G16" s="363" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="H16" s="109"/>
       <c r="I16" s="178"/>
       <c r="J16" s="203" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23757,12 +23775,12 @@
       <c r="E17" s="85"/>
       <c r="F17" s="118"/>
       <c r="G17" s="119" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="H17" s="109"/>
       <c r="I17" s="178"/>
       <c r="J17" s="211" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23771,12 +23789,12 @@
       <c r="E18" s="85"/>
       <c r="F18" s="118"/>
       <c r="G18" s="119" t="s">
-        <v>232</v>
+        <v>330</v>
       </c>
       <c r="H18" s="109"/>
       <c r="I18" s="178"/>
       <c r="J18" s="211" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -23784,12 +23802,12 @@
         <v>196</v>
       </c>
       <c r="D19" s="139" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E19" s="129"/>
       <c r="F19" s="148"/>
       <c r="G19" s="364" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H19" s="140"/>
       <c r="I19" s="361"/>
@@ -23800,9 +23818,7 @@
       <c r="D20" s="144"/>
       <c r="E20" s="130"/>
       <c r="F20" s="202"/>
-      <c r="G20" s="362" t="s">
-        <v>333</v>
-      </c>
+      <c r="G20" s="362"/>
       <c r="H20" s="208"/>
       <c r="I20" s="208"/>
       <c r="J20" s="243"/>
@@ -23812,12 +23828,12 @@
         <v>197</v>
       </c>
       <c r="D21" s="111" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E21" s="85"/>
       <c r="F21" s="122"/>
       <c r="G21" s="120" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H21" s="109"/>
       <c r="J21" s="109"/>
@@ -23827,7 +23843,7 @@
         <v>211</v>
       </c>
       <c r="D22" s="110" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E22" s="85"/>
       <c r="F22" s="118" t="s">
@@ -23843,7 +23859,7 @@
         <v>190</v>
       </c>
       <c r="D23" s="112" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E23" s="85"/>
       <c r="F23" s="109"/>
@@ -23857,7 +23873,7 @@
         <v>183</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E24" s="85"/>
       <c r="F24" s="109"/>
@@ -23871,7 +23887,7 @@
         <v>212</v>
       </c>
       <c r="D25" s="145" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E25" s="129"/>
       <c r="F25" s="140"/>
@@ -23897,7 +23913,7 @@
         <v>203</v>
       </c>
       <c r="D27" s="156" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E27" s="85"/>
       <c r="F27" s="109"/>
@@ -23911,7 +23927,7 @@
         <v>213</v>
       </c>
       <c r="D28" s="114" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E28" s="115"/>
       <c r="F28" s="187" t="s">
@@ -23929,7 +23945,7 @@
         <v>198</v>
       </c>
       <c r="D29" s="110" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E29" s="85"/>
       <c r="F29" s="109"/>
@@ -23943,7 +23959,7 @@
         <v>185</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E30" s="129"/>
       <c r="F30" s="351" t="s">
@@ -23959,7 +23975,7 @@
     <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C31" s="143"/>
       <c r="D31" s="232" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E31" s="233"/>
       <c r="F31" s="234"/>
@@ -23983,7 +23999,7 @@
         <v>198</v>
       </c>
       <c r="D33" s="146" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E33" s="85"/>
       <c r="F33" s="109"/>
@@ -23997,17 +24013,17 @@
         <v>199</v>
       </c>
       <c r="D34" s="110" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E34" s="85"/>
       <c r="F34" s="118"/>
       <c r="G34" s="176" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H34" s="109"/>
       <c r="I34" s="237"/>
       <c r="J34" s="210" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="3:15" ht="20.100000000000001" customHeight="1">
@@ -24033,21 +24049,21 @@
         <v>186</v>
       </c>
       <c r="D36" s="347" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E36" s="130"/>
       <c r="F36" s="202" t="s">
         <v>180</v>
       </c>
       <c r="G36" s="244" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H36" s="348"/>
       <c r="I36" s="349" t="s">
         <v>180</v>
       </c>
       <c r="J36" s="350" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="3:15" ht="20.100000000000001" customHeight="1">
@@ -24056,12 +24072,12 @@
       <c r="E37" s="85"/>
       <c r="F37" s="175"/>
       <c r="G37" s="120" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H37" s="180"/>
       <c r="I37" s="178"/>
       <c r="J37" s="197" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="3:15" ht="20.100000000000001" customHeight="1">
@@ -24069,17 +24085,17 @@
         <v>200</v>
       </c>
       <c r="D38" s="110" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E38" s="85"/>
       <c r="F38" s="175"/>
       <c r="G38" s="120" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H38" s="180"/>
       <c r="I38" s="178"/>
       <c r="J38" s="198" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="3:15" ht="20.100000000000001" customHeight="1">
@@ -24088,12 +24104,12 @@
       <c r="E39" s="85"/>
       <c r="F39" s="118"/>
       <c r="G39" s="238" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H39" s="181"/>
       <c r="I39" s="178"/>
       <c r="J39" s="242" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="3:15" ht="20.100000000000001" customHeight="1">
@@ -24101,17 +24117,17 @@
         <v>190</v>
       </c>
       <c r="D40" s="110" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E40" s="85"/>
       <c r="F40" s="118"/>
       <c r="G40" s="238" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H40" s="181"/>
       <c r="I40" s="182"/>
       <c r="J40" s="197" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O40" s="119"/>
     </row>
@@ -24120,17 +24136,17 @@
         <v>201</v>
       </c>
       <c r="D41" s="139" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E41" s="129"/>
       <c r="F41" s="148"/>
       <c r="G41" s="236" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H41" s="183"/>
       <c r="I41" s="184"/>
       <c r="J41" s="343" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="42" spans="3:15" ht="20.100000000000001" customHeight="1">
@@ -24148,7 +24164,7 @@
         <v>194</v>
       </c>
       <c r="D43" s="110" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E43" s="85"/>
       <c r="F43" s="109"/>
@@ -24162,7 +24178,7 @@
         <v>202</v>
       </c>
       <c r="D44" s="110" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E44" s="85"/>
       <c r="F44" s="109"/>
@@ -24177,7 +24193,7 @@
         <v>193</v>
       </c>
       <c r="D45" s="110" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E45" s="85"/>
       <c r="F45" s="109"/>
@@ -24203,7 +24219,7 @@
         <v>203</v>
       </c>
       <c r="D47" s="157" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E47" s="130"/>
       <c r="F47" s="208"/>
@@ -24211,7 +24227,7 @@
       <c r="H47" s="219"/>
       <c r="I47" s="220"/>
       <c r="J47" s="221" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L47" s="83"/>
     </row>
@@ -24220,7 +24236,7 @@
         <v>204</v>
       </c>
       <c r="D48" s="158" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E48" s="85"/>
       <c r="F48" s="107"/>
@@ -24228,7 +24244,7 @@
       <c r="H48" s="121"/>
       <c r="I48" s="122"/>
       <c r="J48" s="177" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L48" s="83"/>
     </row>
@@ -24237,7 +24253,7 @@
         <v>189</v>
       </c>
       <c r="D49" s="158" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E49" s="85"/>
       <c r="F49" s="108"/>
@@ -24251,7 +24267,7 @@
         <v>191</v>
       </c>
       <c r="D50" s="158" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E50" s="85"/>
       <c r="F50" s="109"/>
@@ -24265,7 +24281,7 @@
         <v>192</v>
       </c>
       <c r="D51" s="159" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E51" s="85"/>
       <c r="H51" s="125"/>
@@ -24275,7 +24291,7 @@
     <row r="52" spans="3:10" ht="20.100000000000001" customHeight="1">
       <c r="C52" s="212"/>
       <c r="D52" s="110" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E52" s="115" t="s">
         <v>110</v>
@@ -24312,7 +24328,7 @@
         <v>180</v>
       </c>
       <c r="G54" s="225" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H54" s="226"/>
       <c r="I54" s="189"/>
@@ -24369,7 +24385,7 @@
         <v>110</v>
       </c>
       <c r="J58" s="218" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="3:10" ht="20.100000000000001" customHeight="1">
@@ -24377,10 +24393,10 @@
       <c r="D59" s="85"/>
       <c r="E59" s="85"/>
       <c r="F59" s="367" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G59" s="368" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H59" s="91"/>
       <c r="I59" s="116"/>
@@ -24460,7 +24476,7 @@
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="1.1417322834645669" bottom="0.55118110236220474" header="0.51181102362204722" footer="0.11811023622047245"/>
   <pageSetup paperSize="8" scale="83" orientation="portrait" cellComments="asDisplayed" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"BIZ UDP明朝 Medium,太字"&amp;22 &amp;U7月19日（日） （本祭）　＜駒寄＞ 進行表&amp;RRev.F</oddHeader>
+    <oddHeader>&amp;C&amp;"BIZ UDP明朝 Medium,太字"&amp;22 &amp;U7月19日（日） （本祭）　＜駒寄＞ 進行表&amp;RRev.G</oddHeader>
   </headerFooter>
   <ignoredErrors>
     <ignoredError sqref="C8:I11 D19:F19 C16:F16 H16:I16 C15:F15 H15:I15 C14:F14 H14:I14 C24:I31 D20:E20 H20 H19 C21:E21 H21 C22:E22 H22:I22 C41:F41 C38:F38 H38:I38 C37:F37 H37:I37 C39:F39 H39:I39 C40:F40 H40:I40 C43:E43 C42:E42 H42 H41:I41 C46:I61 C44:E44 H44 H43 C45:H45 C36:I36 E33:I34 E32:I32 C13:I13 C12:H12 C23 E23:I23 C35:H35" numberStoredAsText="1"/>
